--- a/JsonConverter/ExcelFiles/Evolution.xlsx
+++ b/JsonConverter/ExcelFiles/Evolution.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\바탕화면\Project\Vamsurlike\Vamsurlike\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DC2449F-85E0-4DD5-A7E7-1DA5D2C9F5E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62EE9DEA-F92F-4EF8-928D-140835E20669}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="756" yWindow="1476" windowWidth="28284" windowHeight="14628" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="360" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Enemy" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="478" uniqueCount="386">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="386" uniqueCount="331">
   <si>
     <t>string</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -108,21 +108,6 @@
     <t>Laurel</t>
   </si>
   <si>
-    <t>Bone</t>
-  </si>
-  <si>
-    <t>Cherry Bomb</t>
-  </si>
-  <si>
-    <t>Carréllo</t>
-  </si>
-  <si>
-    <t>Carozza!</t>
-  </si>
-  <si>
-    <t>Celestial Dusting</t>
-  </si>
-  <si>
     <t>None</t>
   </si>
   <si>
@@ -507,132 +492,81 @@
     <t>Celestial Booster</t>
   </si>
   <si>
-    <t>General Information</t>
-  </si>
-  <si>
-    <t>Evolve From</t>
-  </si>
-  <si>
-    <t>Requirements</t>
-  </si>
-  <si>
     <t>Bloody Tear</t>
   </si>
   <si>
-    <t>Starting weapon of Minnah Mannarah Ignores Duration and Speed Scales with Luck</t>
-  </si>
-  <si>
     <t>Hollow Heart</t>
   </si>
   <si>
     <t>Holy Wand</t>
   </si>
   <si>
-    <t>Starting weapon of Leda Ignores Duration</t>
-  </si>
-  <si>
     <t>Empty Tome</t>
   </si>
   <si>
     <t>Thousand Edge</t>
   </si>
   <si>
-    <t>Starting weapon of Boon Marrabbio Malphas starts with it as hidden weapon Ignores Duration</t>
-  </si>
-  <si>
     <t>Bracer</t>
   </si>
   <si>
     <t>Death Spiral</t>
   </si>
   <si>
-    <t>Starting weapon of Mask of the Red Death, Death , and Megalo Death Possible starting weapon of missingN▯ Ignores Duration</t>
-  </si>
-  <si>
     <t>Candelabrador</t>
   </si>
   <si>
     <t>Heaven Sword</t>
   </si>
   <si>
-    <t>Starting weapon of Gains Boros Ignores Duration Scales with Luck</t>
-  </si>
-  <si>
     <t>Clover</t>
   </si>
   <si>
     <t>Unholy Vespers</t>
   </si>
   <si>
-    <t>Scales with all stat bonuses</t>
-  </si>
-  <si>
     <t>Spellbinder</t>
   </si>
   <si>
-    <t>Ignores Duration</t>
-  </si>
-  <si>
     <t>Spinach</t>
   </si>
   <si>
     <t>Soul Eater</t>
   </si>
   <si>
-    <t>Starting weapon of Peppino Ignores Amount, Duration, and Speed</t>
-  </si>
-  <si>
     <t>Pummarola</t>
   </si>
   <si>
     <t>La Borra</t>
   </si>
   <si>
-    <t>Scales with all stat bonuses and Move Speed</t>
-  </si>
-  <si>
     <t>Attractorb</t>
   </si>
   <si>
     <t>NO FUTURE</t>
   </si>
   <si>
-    <t>Starting weapon of Gyoruntin Scales with all stat bonuses and Armor</t>
-  </si>
-  <si>
     <t>Armor</t>
   </si>
   <si>
     <t>Thunder Loop</t>
   </si>
   <si>
-    <t>Ignores Duration and Speed</t>
-  </si>
-  <si>
     <t>Duplicator</t>
   </si>
   <si>
     <t>Gorgeous Moon</t>
   </si>
   <si>
-    <t>Ignores everything but Cooldown</t>
-  </si>
-  <si>
     <t>Crown</t>
   </si>
   <si>
     <t>Vicious Hunger</t>
   </si>
   <si>
-    <t>Starting weapon of Sammy Scales with all stat bonuses and Luck</t>
-  </si>
-  <si>
     <t>Stone Mask</t>
   </si>
   <si>
-    <t>Ignores Speed and Amount</t>
-  </si>
-  <si>
     <t>Skull O'Maniac</t>
   </si>
   <si>
@@ -645,60 +579,21 @@
     <t>Infinite Corridor</t>
   </si>
   <si>
-    <t>Starting weapon of Chaos Ignores Might, Speed, Amount, and Area</t>
-  </si>
-  <si>
     <t>Max Level Silver Ring and Gold Ring</t>
   </si>
   <si>
     <t>Crimson Shroud</t>
   </si>
   <si>
-    <t>Ignores Speed, Duration, and Amount Scales with Armor and Curse</t>
-  </si>
-  <si>
     <t>Max Level Metaglio Left and Metaglio Right</t>
   </si>
   <si>
-    <t>Anima of Mortaccio</t>
-  </si>
-  <si>
-    <t>Requires relic Chaos Malachite and Level 80+ Mortaccio for evolution Acquired automatically when conditions are met</t>
-  </si>
-  <si>
-    <t>Yatta Daikarin</t>
-  </si>
-  <si>
-    <t>Scales with all stat bonuses and Luck</t>
-  </si>
-  <si>
-    <t>Requires relic Chaos Rosalia and Level 80+ Yatta Cavallo for evolution Acquired automatically when conditions are met</t>
-  </si>
-  <si>
-    <t>Requires relic Chaos Lazulia and Level 80+ Bianca Ramba for evolution Acquired automatically when conditions are met</t>
-  </si>
-  <si>
-    <t>Profusione D'Amore</t>
-  </si>
-  <si>
-    <t>Scales with all stat bonuses and Move Speed.</t>
-  </si>
-  <si>
-    <t>Requires relic Chaos Altemanna and Level 80+ O'Sole Meeo for evolution Acquired automatically when conditions are met</t>
-  </si>
-  <si>
-    <t>Scales with all stat bonuses Has a rarity of 20 and a max Level of 6</t>
-  </si>
-  <si>
     <t>Tri-Bracelet</t>
   </si>
   <si>
     <t>Mazo Familiar</t>
   </si>
   <si>
-    <t>Starting weapon of Bats Bats Bats Scales with Max Health Ignores Duration</t>
-  </si>
-  <si>
     <t>Max Level Hollow Heart</t>
   </si>
   <si>
@@ -720,9 +615,6 @@
     <t>Celestial Voulge</t>
   </si>
   <si>
-    <t>Ignores Speed and Duration</t>
-  </si>
-  <si>
     <t>Max Level Wings</t>
   </si>
   <si>
@@ -738,15 +630,9 @@
     <t>Parm Aegis</t>
   </si>
   <si>
-    <t>Starting weapon of Secretino Dagsson</t>
-  </si>
-  <si>
     <t>Karoma's Mana</t>
   </si>
   <si>
-    <t>Starting weapon of Space Dette Ignores Speed and Duration</t>
-  </si>
-  <si>
     <t>Max Level Empty Tome</t>
   </si>
   <si>
@@ -759,9 +645,6 @@
     <t>Godai Shuffle</t>
   </si>
   <si>
-    <t>Ignores Speed</t>
-  </si>
-  <si>
     <t>Max Level Candelabrador</t>
   </si>
   <si>
@@ -774,30 +657,18 @@
     <t>Max Level Attractorb</t>
   </si>
   <si>
-    <t>Ignores Speed and Duration Scales with Luck, Armor and Greed</t>
-  </si>
-  <si>
     <t>Max Level Stone Mask</t>
   </si>
   <si>
     <t>Boo Roo Boolle</t>
   </si>
   <si>
-    <t>Scales with all stat bonuses, Armor, and Move Speed</t>
-  </si>
-  <si>
     <t>Max Level Armor</t>
   </si>
   <si>
-    <t>Ignores Duration Scales with Luck</t>
-  </si>
-  <si>
     <t>Max Level Crown</t>
   </si>
   <si>
-    <t>Ignores Speed Scales with Luck</t>
-  </si>
-  <si>
     <t>Max Level Skull O'Maniac</t>
   </si>
   <si>
@@ -816,9 +687,6 @@
     <t>Paranormal Scan</t>
   </si>
   <si>
-    <t>Ignores Might, Speed, and Duration</t>
-  </si>
-  <si>
     <t>Max Level Mini Ghost</t>
   </si>
   <si>
@@ -951,51 +819,27 @@
     <t>The RPG</t>
   </si>
   <si>
-    <t>Starting weapon of Hammer</t>
-  </si>
-  <si>
     <t>Meal Ticket</t>
   </si>
   <si>
     <t>Max Level Tirajisú</t>
   </si>
   <si>
-    <t>Starting weapon of Dario Bossi</t>
-  </si>
-  <si>
     <t>Max Level Spinach</t>
   </si>
   <si>
-    <t>Starting weapon of Loretta Lecarde</t>
-  </si>
-  <si>
     <t>Pneuma Tempestas</t>
   </si>
   <si>
-    <t>Starting weapon of Stella Lecarde</t>
-  </si>
-  <si>
     <t>Gemma Torpor</t>
   </si>
   <si>
-    <t>Starting weapon of Witch Actrise</t>
-  </si>
-  <si>
     <t>Tenebris Tonitrus</t>
   </si>
   <si>
-    <t>Starting weapon of Galamoth Malphas starts with it as hidden weapon</t>
-  </si>
-  <si>
     <t>Keremet Morbus</t>
   </si>
   <si>
-    <t>Starting weapon of Keremet</t>
-  </si>
-  <si>
-    <t>Starting weapon of Succubus</t>
-  </si>
-  <si>
     <t>Max level Hollow Heart</t>
   </si>
   <si>
@@ -1014,45 +858,27 @@
     <t>Rune Sword</t>
   </si>
   <si>
-    <t>Starting weapon of Joachim Armster</t>
-  </si>
-  <si>
     <t>Alucard Swords</t>
   </si>
   <si>
     <t>Vol Confodere</t>
   </si>
   <si>
-    <t>Has a max Level of 6</t>
-  </si>
-  <si>
     <t>Melio Confodere</t>
   </si>
   <si>
-    <t>Starting weapon of Walter Bernhard</t>
-  </si>
-  <si>
     <t>Max Level Karoma's Mana</t>
   </si>
   <si>
     <t>Rapidus Fio</t>
   </si>
   <si>
-    <t>Starting weapon of Master Librarian .</t>
-  </si>
-  <si>
     <t>Vol Luminatio</t>
   </si>
   <si>
-    <t>Has a max Level of 3</t>
-  </si>
-  <si>
     <t>Vol Umbra</t>
   </si>
   <si>
-    <t>Starting weapon of Graham Jones . Has a max Level of 3</t>
-  </si>
-  <si>
     <t>Claimh Solais</t>
   </si>
   <si>
@@ -1080,9 +906,6 @@
     <t>Pursuant Blades</t>
   </si>
   <si>
-    <t>Has a max Level of 8</t>
-  </si>
-  <si>
     <t>Spellbinder + Dual Whirlwind tech★</t>
   </si>
   <si>
@@ -1150,9 +973,6 @@
   </si>
   <si>
     <t>Blood Chalice</t>
-  </si>
-  <si>
-    <t>Starting weapon of Malevolent Door Spirit Has a max Level of 8</t>
   </si>
   <si>
     <t>Stone Mask + Blood Rage tech★</t>
@@ -1193,6 +1013,26 @@
   </si>
   <si>
     <t>Id</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>EvolveFrom</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>필요 장신구</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>필요 무기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Accessories</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Hollow Heart</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1544,30 +1384,32 @@
   <sheetPr codeName="Sheet1">
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:K1008"/>
+  <dimension ref="A1:I1004"/>
   <sheetFormatPr defaultColWidth="12.5546875" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="12.77734375" style="2" customWidth="1"/>
     <col min="2" max="2" width="19.5546875" style="2" customWidth="1"/>
     <col min="3" max="3" width="13.6640625" style="3" customWidth="1"/>
-    <col min="4" max="4" width="16.88671875" style="3" customWidth="1"/>
-    <col min="5" max="7" width="15.77734375" style="3" customWidth="1"/>
-    <col min="8" max="9" width="15.44140625" style="2" customWidth="1"/>
-    <col min="10" max="10" width="14.77734375" style="2" customWidth="1"/>
-    <col min="11" max="11" width="19.21875" style="2" customWidth="1"/>
-    <col min="12" max="16384" width="12.5546875" style="2"/>
+    <col min="4" max="4" width="15.77734375" style="3" customWidth="1"/>
+    <col min="5" max="5" width="46.33203125" style="3" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="15.44140625" style="2" customWidth="1"/>
+    <col min="8" max="8" width="14.77734375" style="2" customWidth="1"/>
+    <col min="9" max="9" width="19.21875" style="2" customWidth="1"/>
+    <col min="10" max="16384" width="12.5546875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-    </row>
-    <row r="2" spans="1:11" ht="15.6" x14ac:dyDescent="0.35">
+      <c r="D1" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -1578,178 +1420,152 @@
         <v>2</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="F2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="G2" s="2"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
       <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1"/>
-    </row>
-    <row r="3" spans="1:11" ht="15.6" x14ac:dyDescent="0.35">
+    </row>
+    <row r="3" spans="1:9" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
-        <v>385</v>
+        <v>325</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>384</v>
+        <v>324</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>10</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>157</v>
+        <v>326</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="G3" s="2"/>
+        <v>329</v>
+      </c>
+      <c r="F3" s="1"/>
+      <c r="G3" s="1"/>
       <c r="H3" s="1"/>
-      <c r="I3" s="1"/>
-      <c r="J3" s="1"/>
-    </row>
-    <row r="4" spans="1:11" ht="15.6" x14ac:dyDescent="0.35">
+    </row>
+    <row r="4" spans="1:9" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A4" s="11">
         <v>264001</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="C4" s="3">
         <v>40</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>161</v>
+        <v>3</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" ht="15.6" x14ac:dyDescent="0.35">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A5" s="11">
         <v>264002</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>163</v>
+        <v>154</v>
       </c>
       <c r="C5" s="3">
         <v>30</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>164</v>
+        <v>11</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>165</v>
-      </c>
-      <c r="H5" s="5"/>
-      <c r="I5" s="5"/>
-    </row>
-    <row r="6" spans="1:11" ht="15.6" x14ac:dyDescent="0.35">
+        <v>155</v>
+      </c>
+      <c r="F5" s="5"/>
+      <c r="G5" s="5"/>
+    </row>
+    <row r="6" spans="1:9" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A6" s="11">
         <v>264003</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>166</v>
+        <v>156</v>
       </c>
       <c r="C6" s="3">
         <v>16.5</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>167</v>
+        <v>4</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="H6" s="5"/>
-      <c r="I6" s="5"/>
-      <c r="K6" s="3"/>
-    </row>
-    <row r="7" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+        <v>157</v>
+      </c>
+      <c r="F6" s="5"/>
+      <c r="G6" s="5"/>
+      <c r="I6" s="3"/>
+    </row>
+    <row r="7" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="11">
         <v>264004</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>169</v>
+        <v>158</v>
       </c>
       <c r="C7" s="3">
         <v>60</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>170</v>
+        <v>5</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="H7" s="5"/>
-      <c r="I7" s="5"/>
-      <c r="K7" s="3"/>
-    </row>
-    <row r="8" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+        <v>159</v>
+      </c>
+      <c r="F7" s="5"/>
+      <c r="G7" s="5"/>
+      <c r="I7" s="3"/>
+    </row>
+    <row r="8" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="11">
         <v>264005</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>172</v>
+        <v>160</v>
       </c>
       <c r="C8" s="3">
         <v>77</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>173</v>
+        <v>6</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>174</v>
-      </c>
-      <c r="H8" s="3"/>
+        <v>161</v>
+      </c>
+      <c r="F8" s="3"/>
+      <c r="G8" s="3"/>
       <c r="I8" s="3"/>
-      <c r="K8" s="3"/>
-    </row>
-    <row r="9" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="9" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="11">
         <v>264006</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>175</v>
+        <v>162</v>
       </c>
       <c r="C9" s="3">
         <v>30</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>176</v>
+        <v>12</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="H9" s="3"/>
+        <v>163</v>
+      </c>
+      <c r="F9" s="3"/>
+      <c r="G9" s="3"/>
       <c r="I9" s="3"/>
-      <c r="K9" s="3"/>
-    </row>
-    <row r="10" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="10" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="11">
         <v>264007</v>
       </c>
@@ -1760,157 +1576,136 @@
         <v>100</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>178</v>
+        <v>13</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="H10" s="3"/>
+        <v>164</v>
+      </c>
+      <c r="F10" s="3"/>
+      <c r="G10" s="3"/>
       <c r="I10" s="3"/>
-      <c r="K10" s="3"/>
-    </row>
-    <row r="11" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="11" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="11">
         <v>264008</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>180</v>
+        <v>165</v>
       </c>
       <c r="C11" s="3">
         <v>20</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>181</v>
+        <v>7</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="H11" s="3"/>
+        <v>166</v>
+      </c>
+      <c r="F11" s="3"/>
+      <c r="G11" s="3"/>
       <c r="I11" s="3"/>
-      <c r="K11" s="3"/>
-    </row>
-    <row r="12" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="12" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="11">
         <v>264009</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>183</v>
+        <v>167</v>
       </c>
       <c r="C12" s="3">
         <v>40</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>184</v>
+        <v>15</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>185</v>
-      </c>
-      <c r="H12" s="3"/>
+        <v>168</v>
+      </c>
+      <c r="F12" s="3"/>
+      <c r="G12" s="3"/>
       <c r="I12" s="3"/>
-      <c r="K12" s="3"/>
-    </row>
-    <row r="13" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="13" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="11">
         <v>264010</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>186</v>
+        <v>169</v>
       </c>
       <c r="C13" s="3">
         <v>30</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>187</v>
+        <v>8</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F13" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="H13" s="3"/>
+        <v>170</v>
+      </c>
+      <c r="F13" s="3"/>
+      <c r="G13" s="3"/>
       <c r="I13" s="3"/>
-      <c r="K13" s="3"/>
-    </row>
-    <row r="14" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="14" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="11">
         <v>264011</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>189</v>
+        <v>171</v>
       </c>
       <c r="C14" s="3">
         <v>65</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>190</v>
+        <v>16</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>191</v>
-      </c>
-      <c r="H14" s="3"/>
+        <v>172</v>
+      </c>
+      <c r="F14" s="3"/>
+      <c r="G14" s="3"/>
       <c r="I14" s="3"/>
-      <c r="K14" s="3"/>
-    </row>
-    <row r="15" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="15" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="11">
         <v>264012</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>192</v>
+        <v>173</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>17</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>193</v>
+        <v>9</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F15" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="H15" s="3"/>
+        <v>174</v>
+      </c>
+      <c r="F15" s="3"/>
+      <c r="G15" s="3"/>
       <c r="I15" s="3"/>
-      <c r="K15" s="3"/>
-    </row>
-    <row r="16" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="16" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="11">
         <v>264013</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>195</v>
+        <v>175</v>
       </c>
       <c r="C16" s="3">
         <v>30</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>196</v>
+        <v>18</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="F16" s="3" t="s">
-        <v>197</v>
-      </c>
-      <c r="H16" s="3"/>
+        <v>176</v>
+      </c>
+      <c r="F16" s="3"/>
+      <c r="G16" s="3"/>
       <c r="I16" s="3"/>
-      <c r="K16" s="3"/>
-    </row>
-    <row r="17" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="17" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="11">
         <v>264014</v>
       </c>
@@ -1921,2196 +1716,1931 @@
         <v>40</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>198</v>
+        <v>19</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="F17" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="H17" s="3"/>
-      <c r="I17" s="3"/>
-    </row>
-    <row r="18" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+        <v>177</v>
+      </c>
+      <c r="F17" s="3"/>
+      <c r="G17" s="3"/>
+    </row>
+    <row r="18" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="11">
         <v>264015</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>200</v>
+        <v>178</v>
       </c>
       <c r="C18" s="3">
         <v>35</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>184</v>
+        <v>21</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F18" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="H18" s="3"/>
-      <c r="I18" s="3"/>
-    </row>
-    <row r="19" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+        <v>179</v>
+      </c>
+      <c r="F18" s="3"/>
+      <c r="G18" s="3"/>
+    </row>
+    <row r="19" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="11">
         <v>264016</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>202</v>
+        <v>180</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>17</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>203</v>
+        <v>22</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="F19" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="H19" s="3"/>
-      <c r="I19" s="3"/>
-    </row>
-    <row r="20" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+        <v>181</v>
+      </c>
+      <c r="F19" s="3"/>
+      <c r="G19" s="3"/>
+    </row>
+    <row r="20" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="11">
         <v>264017</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>205</v>
+        <v>182</v>
       </c>
       <c r="C20" s="3" t="s">
         <v>17</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>206</v>
+        <v>23</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="F20" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="H20" s="3"/>
-      <c r="I20" s="3"/>
-    </row>
-    <row r="21" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+        <v>183</v>
+      </c>
+      <c r="F20" s="3"/>
+      <c r="G20" s="3"/>
+    </row>
+    <row r="21" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="11">
-        <v>264018</v>
+        <v>264022</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>208</v>
+        <v>26</v>
       </c>
       <c r="C21" s="3">
-        <v>65</v>
+        <v>30</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>176</v>
+        <v>25</v>
       </c>
       <c r="E21" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="F21" s="3" t="s">
+    </row>
+    <row r="22" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="11">
+        <v>264023</v>
+      </c>
+      <c r="B22" s="8" t="s">
+        <v>184</v>
+      </c>
+      <c r="C22" s="3">
+        <v>30</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="11">
+        <v>264024</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="C23" s="3">
+        <v>40</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="11">
+        <v>264025</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C24" s="3">
+        <v>6.5</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="11">
+        <v>264026</v>
+      </c>
+      <c r="B25" s="8" t="s">
+        <v>188</v>
+      </c>
+      <c r="C25" s="3">
+        <v>50</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="11">
+        <v>264027</v>
+      </c>
+      <c r="B26" s="8" t="s">
+        <v>190</v>
+      </c>
+      <c r="C26" s="3">
+        <v>25</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="11">
+        <v>264028</v>
+      </c>
+      <c r="B27" s="8" t="s">
+        <v>192</v>
+      </c>
+      <c r="C27" s="3">
+        <v>20</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="11">
+        <v>264029</v>
+      </c>
+      <c r="B28" s="7" t="s">
+        <v>194</v>
+      </c>
+      <c r="C28" s="3">
+        <v>70</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="F28" s="3"/>
+      <c r="G28" s="3"/>
+      <c r="I28" s="3"/>
+    </row>
+    <row r="29" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="11">
+        <v>264030</v>
+      </c>
+      <c r="B29" s="7" t="s">
+        <v>196</v>
+      </c>
+      <c r="C29" s="3">
+        <v>40</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="F29" s="3"/>
+      <c r="G29" s="3"/>
+      <c r="I29" s="3"/>
+    </row>
+    <row r="30" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A30" s="11">
+        <v>264031</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C30" s="3">
+        <v>10</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A31" s="11">
+        <v>264032</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C31" s="3">
+        <v>25</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A32" s="11">
+        <v>264033</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="C32" s="3">
+        <v>30</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A33" s="11">
+        <v>264034</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="C33" s="3">
+        <v>10</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A34" s="11">
+        <v>264035</v>
+      </c>
+      <c r="B34" s="8" t="s">
+        <v>204</v>
+      </c>
+      <c r="C34" s="3">
+        <v>30</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="E34" s="3" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A35" s="11">
+        <v>264036</v>
+      </c>
+      <c r="B35" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="C35" s="3">
+        <v>60</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A36" s="11">
+        <v>264037</v>
+      </c>
+      <c r="B36" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="C36" s="3">
+        <v>100</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="E36" s="3" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A37" s="11">
+        <v>264038</v>
+      </c>
+      <c r="B37" s="10" t="s">
+        <v>208</v>
+      </c>
+      <c r="C37" s="3">
+        <v>20</v>
+      </c>
+      <c r="D37" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="E37" s="3" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A38" s="11">
+        <v>264039</v>
+      </c>
+      <c r="B38" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="C38" s="3">
+        <v>40</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="E38" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="H21" s="3"/>
-      <c r="I21" s="3"/>
-    </row>
-    <row r="22" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="11">
-        <v>264019</v>
-      </c>
-      <c r="B22" s="8" t="s">
+    </row>
+    <row r="39" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A39" s="11">
+        <v>264040</v>
+      </c>
+      <c r="B39" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="C39" s="3">
+        <v>40</v>
+      </c>
+      <c r="D39" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="E39" s="3" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A40" s="11">
+        <v>264041</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C40" s="3">
+        <v>25</v>
+      </c>
+      <c r="D40" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="E40" s="3" t="s">
         <v>210</v>
       </c>
-      <c r="C22" s="3">
-        <v>20</v>
-      </c>
-      <c r="D22" s="3" t="s">
+    </row>
+    <row r="41" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A41" s="11">
+        <v>264042</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C41" s="3">
+        <v>50</v>
+      </c>
+      <c r="D41" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="E41" s="3" t="s">
         <v>211</v>
       </c>
-      <c r="E22" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F22" s="3" t="s">
+    </row>
+    <row r="42" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A42" s="11">
+        <v>264043</v>
+      </c>
+      <c r="B42" s="2" t="s">
         <v>212</v>
       </c>
-      <c r="H22" s="3"/>
-      <c r="I22" s="3"/>
-    </row>
-    <row r="23" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="11">
-        <v>264020</v>
-      </c>
-      <c r="B23" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="C23" s="3">
-        <v>150</v>
-      </c>
-      <c r="D23" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="E23" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F23" s="3" t="s">
+      <c r="C42" s="3">
+        <v>45</v>
+      </c>
+      <c r="D42" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="E42" s="3" t="s">
         <v>213</v>
       </c>
-      <c r="H23" s="3"/>
-      <c r="I23" s="3"/>
-    </row>
-    <row r="24" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="11">
-        <v>264021</v>
-      </c>
-      <c r="B24" s="7" t="s">
+    </row>
+    <row r="43" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A43" s="11">
+        <v>264044</v>
+      </c>
+      <c r="B43" s="2" t="s">
         <v>214</v>
-      </c>
-      <c r="C24" s="3">
-        <v>10</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>215</v>
-      </c>
-      <c r="E24" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="F24" s="3" t="s">
-        <v>216</v>
-      </c>
-      <c r="H24" s="3"/>
-      <c r="I24" s="3"/>
-    </row>
-    <row r="25" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="11">
-        <v>264022</v>
-      </c>
-      <c r="B25" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="C25" s="3">
-        <v>30</v>
-      </c>
-      <c r="D25" s="3" t="s">
-        <v>217</v>
-      </c>
-      <c r="E25" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="F25" s="3" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="26" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="11">
-        <v>264023</v>
-      </c>
-      <c r="B26" s="8" t="s">
-        <v>218</v>
-      </c>
-      <c r="C26" s="3">
-        <v>30</v>
-      </c>
-      <c r="D26" s="3" t="s">
-        <v>217</v>
-      </c>
-      <c r="E26" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="F26" s="3" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="27" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="11">
-        <v>264024</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>219</v>
-      </c>
-      <c r="C27" s="3">
-        <v>40</v>
-      </c>
-      <c r="D27" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="E27" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="F27" s="3" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="28" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="11">
-        <v>264025</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="C28" s="3">
-        <v>6.5</v>
-      </c>
-      <c r="E28" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="F28" s="3" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="29" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="11">
-        <v>264026</v>
-      </c>
-      <c r="B29" s="8" t="s">
-        <v>223</v>
-      </c>
-      <c r="C29" s="3">
-        <v>50</v>
-      </c>
-      <c r="D29" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="E29" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="30" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="11">
-        <v>264027</v>
-      </c>
-      <c r="B30" s="8" t="s">
-        <v>225</v>
-      </c>
-      <c r="C30" s="3">
-        <v>25</v>
-      </c>
-      <c r="E30" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="F30" s="3" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="31" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="11">
-        <v>264028</v>
-      </c>
-      <c r="B31" s="8" t="s">
-        <v>227</v>
-      </c>
-      <c r="C31" s="3">
-        <v>20</v>
-      </c>
-      <c r="D31" s="3" t="s">
-        <v>228</v>
-      </c>
-      <c r="E31" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="F31" s="3" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="32" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="11">
-        <v>264029</v>
-      </c>
-      <c r="B32" s="7" t="s">
-        <v>230</v>
-      </c>
-      <c r="C32" s="3">
-        <v>70</v>
-      </c>
-      <c r="E32" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F32" s="3" t="s">
-        <v>231</v>
-      </c>
-      <c r="H32" s="3"/>
-      <c r="I32" s="3"/>
-      <c r="K32" s="3"/>
-    </row>
-    <row r="33" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="11">
-        <v>264030</v>
-      </c>
-      <c r="B33" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="C33" s="3">
-        <v>40</v>
-      </c>
-      <c r="E33" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="F33" s="3" t="s">
-        <v>233</v>
-      </c>
-      <c r="H33" s="3"/>
-      <c r="I33" s="3"/>
-      <c r="K33" s="3"/>
-    </row>
-    <row r="34" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="11">
-        <v>264031</v>
-      </c>
-      <c r="B34" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="C34" s="3">
-        <v>10</v>
-      </c>
-      <c r="D34" s="3" t="s">
-        <v>234</v>
-      </c>
-      <c r="E34" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="F34" s="3" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="35" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A35" s="11">
-        <v>264032</v>
-      </c>
-      <c r="B35" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="C35" s="3">
-        <v>25</v>
-      </c>
-      <c r="D35" s="3" t="s">
-        <v>236</v>
-      </c>
-      <c r="E35" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F35" s="3" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="36" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="11">
-        <v>264033</v>
-      </c>
-      <c r="B36" s="2" t="s">
-        <v>238</v>
-      </c>
-      <c r="C36" s="3">
-        <v>30</v>
-      </c>
-      <c r="D36" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="E36" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="F36" s="3" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="37" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="11">
-        <v>264034</v>
-      </c>
-      <c r="B37" s="2" t="s">
-        <v>240</v>
-      </c>
-      <c r="C37" s="3">
-        <v>10</v>
-      </c>
-      <c r="D37" s="3" t="s">
-        <v>241</v>
-      </c>
-      <c r="E37" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="F37" s="3" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="38" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="11">
-        <v>264035</v>
-      </c>
-      <c r="B38" s="8" t="s">
-        <v>243</v>
-      </c>
-      <c r="C38" s="3">
-        <v>30</v>
-      </c>
-      <c r="D38" s="3" t="s">
-        <v>241</v>
-      </c>
-      <c r="E38" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="F38" s="3" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="39" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="11">
-        <v>264036</v>
-      </c>
-      <c r="B39" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="C39" s="3">
-        <v>60</v>
-      </c>
-      <c r="D39" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="E39" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="F39" s="3" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="40" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="11">
-        <v>264037</v>
-      </c>
-      <c r="B40" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="C40" s="3">
-        <v>100</v>
-      </c>
-      <c r="D40" s="3" t="s">
-        <v>246</v>
-      </c>
-      <c r="E40" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="F40" s="3" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="41" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A41" s="11">
-        <v>264038</v>
-      </c>
-      <c r="B41" s="10" t="s">
-        <v>248</v>
-      </c>
-      <c r="C41" s="3">
-        <v>20</v>
-      </c>
-      <c r="D41" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="E41" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="F41" s="3" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="42" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A42" s="11">
-        <v>264039</v>
-      </c>
-      <c r="B42" s="10" t="s">
-        <v>53</v>
-      </c>
-      <c r="C42" s="3">
-        <v>40</v>
-      </c>
-      <c r="D42" s="3" t="s">
-        <v>249</v>
-      </c>
-      <c r="E42" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="F42" s="3" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="43" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A43" s="11">
-        <v>264040</v>
-      </c>
-      <c r="B43" s="10" t="s">
-        <v>55</v>
       </c>
       <c r="C43" s="3">
         <v>40</v>
       </c>
       <c r="D43" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A44" s="11">
+        <v>264045</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D44" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A45" s="11">
+        <v>264046</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="C45" s="3">
+        <v>100</v>
+      </c>
+      <c r="D45" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A46" s="11">
+        <v>264047</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="C46" s="3">
+        <v>50</v>
+      </c>
+      <c r="D46" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E46" s="3" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A47" s="11">
+        <v>264048</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="C47" s="3">
+        <v>45</v>
+      </c>
+      <c r="D47" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A48" s="11">
+        <v>264049</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="C48" s="3">
+        <v>20</v>
+      </c>
+      <c r="D48" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="E48" s="3" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A49" s="11">
+        <v>264050</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="C49" s="3">
+        <v>10</v>
+      </c>
+      <c r="D49" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="E49" s="3" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A50" s="11">
+        <v>264051</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="C50" s="3">
+        <v>60</v>
+      </c>
+      <c r="D50" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="E50" s="3" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A51" s="11">
+        <v>264052</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="C51" s="3">
+        <v>35</v>
+      </c>
+      <c r="D51" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="E51" s="3" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A52" s="11">
+        <v>264053</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="C52" s="3">
+        <v>25</v>
+      </c>
+      <c r="D52" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A53" s="11">
+        <v>264054</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C53" s="3">
+        <v>28</v>
+      </c>
+      <c r="D53" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="E53" s="3" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A54" s="11">
+        <v>264055</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="C54" s="3">
+        <v>30</v>
+      </c>
+      <c r="D54" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="E54" s="3" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A55" s="11">
+        <v>264056</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="C55" s="3">
+        <v>40</v>
+      </c>
+      <c r="D55" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="E55" s="3" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A56" s="11">
+        <v>264057</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="C56" s="3">
+        <v>40</v>
+      </c>
+      <c r="D56" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="E56" s="3" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A57" s="11">
+        <v>264058</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="C57" s="3">
+        <v>24</v>
+      </c>
+      <c r="D57" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="E57" s="3" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A58" s="11">
+        <v>264059</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="C58" s="3">
+        <v>10</v>
+      </c>
+      <c r="D58" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="E58" s="3" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A59" s="11">
+        <v>264060</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="C59" s="3">
+        <v>60</v>
+      </c>
+      <c r="D59" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="E59" s="3" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A60" s="11">
+        <v>264061</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="C60" s="3">
+        <v>80</v>
+      </c>
+      <c r="D60" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="E60" s="3" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A61" s="11">
+        <v>264062</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="C61" s="3">
+        <v>30</v>
+      </c>
+      <c r="D61" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="E61" s="3" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A62" s="11">
+        <v>264063</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="C62" s="3">
+        <v>50</v>
+      </c>
+      <c r="D62" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A63" s="11">
+        <v>264064</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="C63" s="3">
+        <v>40</v>
+      </c>
+      <c r="D63" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="E63" s="3" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A64" s="11">
+        <v>264065</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="C64" s="3">
+        <v>25</v>
+      </c>
+      <c r="D64" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="E64" s="3" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A65" s="11">
+        <v>264066</v>
+      </c>
+      <c r="B65" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="C65" s="3">
+        <v>40</v>
+      </c>
+      <c r="D65" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="E65" s="3" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A66" s="11">
+        <v>264067</v>
+      </c>
+      <c r="B66" s="2" t="s">
         <v>251</v>
       </c>
-      <c r="E43" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="F43" s="3" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="44" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A44" s="11">
-        <v>264041</v>
-      </c>
-      <c r="B44" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="C44" s="3">
-        <v>25</v>
-      </c>
-      <c r="D44" s="3" t="s">
-        <v>190</v>
-      </c>
-      <c r="E44" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="F44" s="3" t="s">
+      <c r="C66" s="3">
+        <v>60</v>
+      </c>
+      <c r="D66" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="E66" s="3" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A67" s="11">
+        <v>264068</v>
+      </c>
+      <c r="B67" s="2" t="s">
         <v>252</v>
-      </c>
-    </row>
-    <row r="45" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A45" s="11">
-        <v>264042</v>
-      </c>
-      <c r="B45" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="C45" s="3">
-        <v>50</v>
-      </c>
-      <c r="D45" s="3" t="s">
-        <v>253</v>
-      </c>
-      <c r="E45" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="F45" s="3" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="46" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A46" s="11">
-        <v>264043</v>
-      </c>
-      <c r="B46" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="C46" s="3">
-        <v>45</v>
-      </c>
-      <c r="D46" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="E46" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="F46" s="3" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="47" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A47" s="11">
-        <v>264044</v>
-      </c>
-      <c r="B47" s="2" t="s">
-        <v>257</v>
-      </c>
-      <c r="C47" s="3">
-        <v>40</v>
-      </c>
-      <c r="D47" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="E47" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="F47" s="3" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="48" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A48" s="11">
-        <v>264045</v>
-      </c>
-      <c r="B48" s="2" t="s">
-        <v>259</v>
-      </c>
-      <c r="C48" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D48" s="3" t="s">
-        <v>260</v>
-      </c>
-      <c r="E48" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="F48" s="3" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A49" s="11">
-        <v>264046</v>
-      </c>
-      <c r="B49" s="2" t="s">
-        <v>262</v>
-      </c>
-      <c r="C49" s="3">
-        <v>100</v>
-      </c>
-      <c r="D49" s="3" t="s">
-        <v>241</v>
-      </c>
-      <c r="E49" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="F49" s="3" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A50" s="11">
-        <v>264047</v>
-      </c>
-      <c r="B50" s="2" t="s">
-        <v>264</v>
-      </c>
-      <c r="C50" s="3">
-        <v>50</v>
-      </c>
-      <c r="D50" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="E50" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="F50" s="3" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A51" s="11">
-        <v>264048</v>
-      </c>
-      <c r="B51" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="C51" s="3">
-        <v>45</v>
-      </c>
-      <c r="D51" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="E51" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="F51" s="3" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A52" s="11">
-        <v>264049</v>
-      </c>
-      <c r="B52" s="2" t="s">
-        <v>267</v>
-      </c>
-      <c r="C52" s="3">
-        <v>20</v>
-      </c>
-      <c r="D52" s="3" t="s">
-        <v>241</v>
-      </c>
-      <c r="E52" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="F52" s="3" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A53" s="11">
-        <v>264050</v>
-      </c>
-      <c r="B53" s="2" t="s">
-        <v>269</v>
-      </c>
-      <c r="C53" s="3">
-        <v>10</v>
-      </c>
-      <c r="D53" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="E53" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="F53" s="3" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A54" s="11">
-        <v>264051</v>
-      </c>
-      <c r="B54" s="2" t="s">
-        <v>271</v>
-      </c>
-      <c r="C54" s="3">
-        <v>60</v>
-      </c>
-      <c r="D54" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="E54" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="F54" s="3" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A55" s="11">
-        <v>264052</v>
-      </c>
-      <c r="B55" s="2" t="s">
-        <v>273</v>
-      </c>
-      <c r="C55" s="3">
-        <v>35</v>
-      </c>
-      <c r="D55" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="E55" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="F55" s="3" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A56" s="11">
-        <v>264053</v>
-      </c>
-      <c r="B56" s="2" t="s">
-        <v>275</v>
-      </c>
-      <c r="C56" s="3">
-        <v>25</v>
-      </c>
-      <c r="D56" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="E56" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="F56" s="3" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A57" s="11">
-        <v>264054</v>
-      </c>
-      <c r="B57" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="C57" s="3">
-        <v>28</v>
-      </c>
-      <c r="E57" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="F57" s="3" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A58" s="11">
-        <v>264055</v>
-      </c>
-      <c r="B58" s="2" t="s">
-        <v>278</v>
-      </c>
-      <c r="C58" s="3">
-        <v>30</v>
-      </c>
-      <c r="E58" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="F58" s="3" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A59" s="11">
-        <v>264056</v>
-      </c>
-      <c r="B59" s="2" t="s">
-        <v>280</v>
-      </c>
-      <c r="C59" s="3">
-        <v>40</v>
-      </c>
-      <c r="D59" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="E59" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="F59" s="3" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A60" s="11">
-        <v>264057</v>
-      </c>
-      <c r="B60" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="C60" s="3">
-        <v>40</v>
-      </c>
-      <c r="E60" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="F60" s="3" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="61" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A61" s="11">
-        <v>264058</v>
-      </c>
-      <c r="B61" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="C61" s="3">
-        <v>24</v>
-      </c>
-      <c r="E61" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="F61" s="3" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="62" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A62" s="11">
-        <v>264059</v>
-      </c>
-      <c r="B62" s="2" t="s">
-        <v>284</v>
-      </c>
-      <c r="C62" s="3">
-        <v>10</v>
-      </c>
-      <c r="E62" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="F62" s="3" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="63" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A63" s="11">
-        <v>264060</v>
-      </c>
-      <c r="B63" s="2" t="s">
-        <v>286</v>
-      </c>
-      <c r="C63" s="3">
-        <v>60</v>
-      </c>
-      <c r="D63" s="3" t="s">
-        <v>228</v>
-      </c>
-      <c r="E63" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="F63" s="3" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="64" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A64" s="11">
-        <v>264061</v>
-      </c>
-      <c r="B64" s="2" t="s">
-        <v>288</v>
-      </c>
-      <c r="C64" s="3">
-        <v>80</v>
-      </c>
-      <c r="E64" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="F64" s="3" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="65" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A65" s="11">
-        <v>264062</v>
-      </c>
-      <c r="B65" s="2" t="s">
-        <v>290</v>
-      </c>
-      <c r="C65" s="3">
-        <v>30</v>
-      </c>
-      <c r="E65" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="F65" s="3" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="66" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A66" s="11">
-        <v>264063</v>
-      </c>
-      <c r="B66" s="2" t="s">
-        <v>291</v>
-      </c>
-      <c r="C66" s="3">
-        <v>50</v>
-      </c>
-      <c r="E66" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="F66" s="3" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="67" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A67" s="11">
-        <v>264064</v>
-      </c>
-      <c r="B67" s="2" t="s">
-        <v>292</v>
       </c>
       <c r="C67" s="3">
         <v>40</v>
       </c>
+      <c r="D67" s="3" t="s">
+        <v>84</v>
+      </c>
       <c r="E67" s="3" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A68" s="11">
+        <v>264069</v>
+      </c>
+      <c r="B68" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="C68" s="3">
+        <v>20</v>
+      </c>
+      <c r="D68" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="F67" s="3" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="68" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A68" s="11">
-        <v>264065</v>
-      </c>
-      <c r="B68" s="2" t="s">
-        <v>293</v>
-      </c>
-      <c r="C68" s="3">
-        <v>25</v>
-      </c>
       <c r="E68" s="3" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A69" s="11">
+        <v>264070</v>
+      </c>
+      <c r="B69" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="C69" s="3">
+        <v>20</v>
+      </c>
+      <c r="D69" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="F68" s="3" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="69" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A69" s="11">
-        <v>264066</v>
-      </c>
-      <c r="B69" s="2" t="s">
-        <v>294</v>
-      </c>
-      <c r="C69" s="3">
+      <c r="E69" s="3" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A70" s="11">
+        <v>264071</v>
+      </c>
+      <c r="B70" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="C70" s="3">
+        <v>30</v>
+      </c>
+      <c r="D70" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="E70" s="3" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A71" s="11">
+        <v>264072</v>
+      </c>
+      <c r="B71" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="C71" s="3">
+        <v>30</v>
+      </c>
+      <c r="D71" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="E71" s="3" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A72" s="11">
+        <v>264073</v>
+      </c>
+      <c r="B72" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="C72" s="3">
+        <v>100</v>
+      </c>
+      <c r="D72" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="E72" s="3" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A73" s="11">
+        <v>264074</v>
+      </c>
+      <c r="B73" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="C73" s="3">
+        <v>100</v>
+      </c>
+      <c r="D73" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="E73" s="3" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A74" s="11">
+        <v>264075</v>
+      </c>
+      <c r="B74" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="C74" s="3">
         <v>40</v>
       </c>
-      <c r="E69" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="F69" s="3" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="70" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A70" s="11">
-        <v>264067</v>
-      </c>
-      <c r="B70" s="2" t="s">
-        <v>295</v>
-      </c>
-      <c r="C70" s="3">
-        <v>60</v>
-      </c>
-      <c r="E70" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="F70" s="3" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="71" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A71" s="11">
-        <v>264068</v>
-      </c>
-      <c r="B71" s="2" t="s">
-        <v>296</v>
-      </c>
-      <c r="C71" s="3">
-        <v>40</v>
-      </c>
-      <c r="E71" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="F71" s="3" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="72" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A72" s="11">
-        <v>264069</v>
-      </c>
-      <c r="B72" s="2" t="s">
-        <v>297</v>
-      </c>
-      <c r="C72" s="3">
+      <c r="D74" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="E74" s="3" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A75" s="11">
+        <v>264076</v>
+      </c>
+      <c r="B75" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="C75" s="3">
+        <v>15</v>
+      </c>
+      <c r="D75" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="E75" s="3" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A76" s="11">
+        <v>264077</v>
+      </c>
+      <c r="B76" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="C76" s="3">
         <v>20</v>
       </c>
-      <c r="E72" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="F72" s="3" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="73" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A73" s="11">
-        <v>264070</v>
-      </c>
-      <c r="B73" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="C73" s="3">
+      <c r="D76" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="E76" s="3" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A77" s="11">
+        <v>264078</v>
+      </c>
+      <c r="B77" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="C77" s="3">
+        <v>5</v>
+      </c>
+      <c r="D77" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="E77" s="3" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A78" s="11">
+        <v>264079</v>
+      </c>
+      <c r="B78" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="C78" s="3">
         <v>20</v>
       </c>
-      <c r="E73" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="F73" s="3" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="74" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A74" s="11">
-        <v>264071</v>
-      </c>
-      <c r="B74" s="2" t="s">
-        <v>299</v>
-      </c>
-      <c r="C74" s="3">
-        <v>30</v>
-      </c>
-      <c r="E74" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="F74" s="3" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="75" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A75" s="11">
-        <v>264072</v>
-      </c>
-      <c r="B75" s="2" t="s">
-        <v>300</v>
-      </c>
-      <c r="C75" s="3">
-        <v>30</v>
-      </c>
-      <c r="E75" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="F75" s="3" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="76" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A76" s="11">
-        <v>264073</v>
-      </c>
-      <c r="B76" s="2" t="s">
-        <v>302</v>
-      </c>
-      <c r="C76" s="3">
-        <v>100</v>
-      </c>
-      <c r="E76" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="F76" s="3" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="77" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A77" s="11">
-        <v>264074</v>
-      </c>
-      <c r="B77" s="2" t="s">
-        <v>303</v>
-      </c>
-      <c r="C77" s="3">
-        <v>100</v>
-      </c>
-      <c r="E77" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="F77" s="3" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="78" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A78" s="11">
-        <v>264075</v>
-      </c>
-      <c r="B78" s="2" t="s">
-        <v>304</v>
-      </c>
-      <c r="C78" s="3">
-        <v>40</v>
-      </c>
       <c r="D78" s="3" t="s">
-        <v>305</v>
+        <v>97</v>
       </c>
       <c r="E78" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="F78" s="3" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="79" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A79" s="11">
-        <v>264076</v>
+        <v>264080</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>306</v>
+        <v>265</v>
       </c>
       <c r="C79" s="3">
-        <v>15</v>
+        <v>50</v>
+      </c>
+      <c r="D79" s="3" t="s">
+        <v>98</v>
       </c>
       <c r="E79" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="F79" s="3" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="80" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A80" s="11">
-        <v>264077</v>
+        <v>264081</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>99</v>
+        <v>266</v>
       </c>
       <c r="C80" s="3">
         <v>20</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>308</v>
+        <v>99</v>
       </c>
       <c r="E80" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="F80" s="3" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="81" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A81" s="11">
-        <v>264078</v>
+        <v>264082</v>
       </c>
       <c r="B81" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="C81" s="3">
+        <v>20</v>
+      </c>
+      <c r="D81" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="E81" s="3" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A82" s="11">
+        <v>264083</v>
+      </c>
+      <c r="B82" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="C82" s="3">
+        <v>25</v>
+      </c>
+      <c r="D82" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="C81" s="3">
-        <v>5</v>
-      </c>
-      <c r="D81" s="3" t="s">
-        <v>310</v>
-      </c>
-      <c r="E81" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="F81" s="3" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="82" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A82" s="11">
-        <v>264079</v>
-      </c>
-      <c r="B82" s="2" t="s">
-        <v>311</v>
-      </c>
-      <c r="C82" s="3">
-        <v>20</v>
-      </c>
-      <c r="D82" s="3" t="s">
-        <v>312</v>
-      </c>
       <c r="E82" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="F82" s="3" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="83" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A83" s="11">
-        <v>264080</v>
+        <v>264084</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>313</v>
+        <v>104</v>
       </c>
       <c r="C83" s="3">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>314</v>
+        <v>103</v>
       </c>
       <c r="E83" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="F83" s="3" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="84" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A84" s="11">
-        <v>264081</v>
+        <v>264085</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>315</v>
+        <v>106</v>
       </c>
       <c r="C84" s="3">
-        <v>20</v>
+        <v>80</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>316</v>
+        <v>105</v>
       </c>
       <c r="E84" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="F84" s="3" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="85" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A85" s="11">
-        <v>264082</v>
+        <v>264086</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>317</v>
+        <v>269</v>
       </c>
       <c r="C85" s="3">
         <v>20</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>318</v>
+        <v>107</v>
       </c>
       <c r="E85" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="F85" s="3" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="86" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A86" s="11">
-        <v>264083</v>
+        <v>264087</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>107</v>
+        <v>270</v>
       </c>
       <c r="C86" s="3">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>319</v>
+        <v>108</v>
       </c>
       <c r="E86" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="F86" s="3" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="87" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A87" s="11">
-        <v>264084</v>
+        <v>264088</v>
       </c>
       <c r="B87" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="C87" s="3">
+        <v>40</v>
+      </c>
+      <c r="D87" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="C87" s="3">
-        <v>10</v>
-      </c>
       <c r="E87" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="F87" s="3" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="88" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A88" s="11">
-        <v>264085</v>
+        <v>264089</v>
       </c>
       <c r="B88" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="C88" s="3">
+        <v>20</v>
+      </c>
+      <c r="D88" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="C88" s="3">
-        <v>80</v>
-      </c>
       <c r="E88" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="F88" s="3" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="89" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A89" s="11">
-        <v>264086</v>
+        <v>264090</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>321</v>
+        <v>272</v>
       </c>
       <c r="C89" s="3">
         <v>20</v>
       </c>
+      <c r="D89" s="3" t="s">
+        <v>112</v>
+      </c>
       <c r="E89" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="F89" s="3" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="90" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A90" s="11">
-        <v>264087</v>
+        <v>264091</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>322</v>
+        <v>273</v>
       </c>
       <c r="C90" s="3">
+        <v>90</v>
+      </c>
+      <c r="D90" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="E90" s="3" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A91" s="11">
+        <v>264092</v>
+      </c>
+      <c r="B91" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="C91" s="3">
         <v>50</v>
       </c>
-      <c r="E90" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="F90" s="3" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="91" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A91" s="11">
-        <v>264088</v>
-      </c>
-      <c r="B91" s="2" t="s">
+      <c r="D91" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="E91" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A92" s="11">
+        <v>264093</v>
+      </c>
+      <c r="B92" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="C92" s="3">
+        <v>10</v>
+      </c>
+      <c r="D92" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="C91" s="3">
-        <v>40</v>
-      </c>
-      <c r="E91" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="F91" s="3" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="92" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A92" s="11">
-        <v>264089</v>
-      </c>
-      <c r="B92" s="2" t="s">
-        <v>323</v>
-      </c>
-      <c r="C92" s="3">
+      <c r="E92" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A93" s="11">
+        <v>264094</v>
+      </c>
+      <c r="B93" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="C93" s="3">
+        <v>14</v>
+      </c>
+      <c r="D93" s="3" t="s">
+        <v>275</v>
+      </c>
+      <c r="E93" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A94" s="11">
+        <v>264095</v>
+      </c>
+      <c r="B94" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="C94" s="3">
         <v>20</v>
       </c>
-      <c r="E92" s="3" t="s">
+      <c r="D94" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="F92" s="3" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="93" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A93" s="11">
-        <v>264090</v>
-      </c>
-      <c r="B93" s="2" t="s">
-        <v>324</v>
-      </c>
-      <c r="C93" s="3">
-        <v>20</v>
-      </c>
-      <c r="E93" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="F93" s="3" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="94" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A94" s="11">
-        <v>264091</v>
-      </c>
-      <c r="B94" s="2" t="s">
-        <v>325</v>
-      </c>
-      <c r="C94" s="3">
-        <v>90</v>
-      </c>
-      <c r="D94" s="3" t="s">
-        <v>326</v>
-      </c>
       <c r="E94" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="F94" s="3" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="95" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A95" s="11">
-        <v>264092</v>
+        <v>264096</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>327</v>
+        <v>119</v>
       </c>
       <c r="C95" s="3">
         <v>50</v>
       </c>
+      <c r="D95" s="3" t="s">
+        <v>118</v>
+      </c>
       <c r="E95" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="F95" s="3" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="96" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A96" s="11">
-        <v>264093</v>
+        <v>264097</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>328</v>
+        <v>278</v>
       </c>
       <c r="C96" s="3">
         <v>10</v>
       </c>
       <c r="D96" s="3" t="s">
-        <v>329</v>
+        <v>120</v>
       </c>
       <c r="E96" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="F96" s="3" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="97" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A97" s="11">
-        <v>264094</v>
+        <v>264098</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>330</v>
+        <v>279</v>
       </c>
       <c r="C97" s="3">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D97" s="3" t="s">
-        <v>329</v>
+        <v>121</v>
       </c>
       <c r="E97" s="3" t="s">
-        <v>328</v>
-      </c>
-      <c r="F97" s="3" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="98" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A98" s="11">
-        <v>264095</v>
+        <v>264099</v>
       </c>
       <c r="B98" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="C98" s="3">
+        <v>12</v>
+      </c>
+      <c r="D98" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="C98" s="3">
+      <c r="E98" s="3" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A99" s="11">
+        <v>264100</v>
+      </c>
+      <c r="B99" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="C99" s="3">
+        <v>77</v>
+      </c>
+      <c r="D99" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="E99" s="3" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A100" s="11">
+        <v>264101</v>
+      </c>
+      <c r="B100" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="C100" s="3">
+        <v>12</v>
+      </c>
+      <c r="D100" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="E100" s="3" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A101" s="11">
+        <v>264102</v>
+      </c>
+      <c r="B101" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="C101" s="3">
+        <v>18</v>
+      </c>
+      <c r="D101" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A102" s="11">
+        <v>264103</v>
+      </c>
+      <c r="B102" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="C102" s="3">
+        <v>12.5</v>
+      </c>
+      <c r="D102" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="E102" s="3" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A103" s="11">
+        <v>264104</v>
+      </c>
+      <c r="B103" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="C103" s="3">
         <v>20</v>
       </c>
-      <c r="D98" s="3" t="s">
-        <v>331</v>
-      </c>
-      <c r="E98" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="F98" s="3" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="99" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A99" s="11">
-        <v>264096</v>
-      </c>
-      <c r="B99" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="C99" s="3">
-        <v>50</v>
-      </c>
-      <c r="E99" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="F99" s="3" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="100" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A100" s="11">
-        <v>264097</v>
-      </c>
-      <c r="B100" s="2" t="s">
-        <v>333</v>
-      </c>
-      <c r="C100" s="3">
-        <v>10</v>
-      </c>
-      <c r="D100" s="3" t="s">
-        <v>334</v>
-      </c>
-      <c r="E100" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="F100" s="3" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="101" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A101" s="11">
-        <v>264098</v>
-      </c>
-      <c r="B101" s="2" t="s">
-        <v>335</v>
-      </c>
-      <c r="C101" s="3">
-        <v>12</v>
-      </c>
-      <c r="D101" s="3" t="s">
-        <v>336</v>
-      </c>
-      <c r="E101" s="3" t="s">
+      <c r="D103" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="F101" s="3" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="102" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A102" s="11">
-        <v>264099</v>
-      </c>
-      <c r="B102" s="2" t="s">
-        <v>337</v>
-      </c>
-      <c r="C102" s="3">
-        <v>12</v>
-      </c>
-      <c r="D102" s="3" t="s">
-        <v>338</v>
-      </c>
-      <c r="E102" s="3" t="s">
+      <c r="E103" s="3" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A104" s="11">
+        <v>264105</v>
+      </c>
+      <c r="B104" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="C104" s="3">
+        <v>40</v>
+      </c>
+      <c r="D104" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="F102" s="3" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="103" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A103" s="11">
-        <v>264100</v>
-      </c>
-      <c r="B103" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="C103" s="3">
-        <v>77</v>
-      </c>
-      <c r="E103" s="3" t="s">
+      <c r="E104" s="3" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A105" s="11">
+        <v>264106</v>
+      </c>
+      <c r="B105" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="C105" s="3">
+        <v>30</v>
+      </c>
+      <c r="D105" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="F103" s="3" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="104" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A104" s="11">
-        <v>264101</v>
-      </c>
-      <c r="B104" s="2" t="s">
-        <v>340</v>
-      </c>
-      <c r="C104" s="3">
-        <v>12</v>
-      </c>
-      <c r="D104" s="3" t="s">
-        <v>329</v>
-      </c>
-      <c r="E104" s="3" t="s">
+      <c r="E105" s="3" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A106" s="11">
+        <v>264107</v>
+      </c>
+      <c r="B106" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="C106" s="3">
+        <v>60</v>
+      </c>
+      <c r="D106" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="F104" s="3" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="105" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A105" s="11">
-        <v>264102</v>
-      </c>
-      <c r="B105" s="2" t="s">
-        <v>342</v>
-      </c>
-      <c r="C105" s="3">
-        <v>18</v>
-      </c>
-      <c r="E105" s="3" t="s">
-        <v>340</v>
-      </c>
-      <c r="F105" s="3" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="106" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A106" s="11">
-        <v>264103</v>
-      </c>
-      <c r="B106" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="C106" s="3">
-        <v>12.5</v>
-      </c>
-      <c r="D106" s="3" t="s">
-        <v>329</v>
-      </c>
       <c r="E106" s="3" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A107" s="11">
+        <v>264108</v>
+      </c>
+      <c r="B107" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="C107" s="3">
+        <v>6.5</v>
+      </c>
+      <c r="D107" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="F106" s="3" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="107" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A107" s="11">
-        <v>264104</v>
-      </c>
-      <c r="B107" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="C107" s="3">
-        <v>20</v>
-      </c>
       <c r="E107" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="F107" s="3" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="108" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A108" s="11">
-        <v>264105</v>
+        <v>264109</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>347</v>
+        <v>296</v>
       </c>
       <c r="C108" s="3">
-        <v>40</v>
+        <v>16.5</v>
       </c>
       <c r="D108" s="3" t="s">
-        <v>348</v>
+        <v>294</v>
       </c>
       <c r="E108" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="F108" s="3" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="109" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A109" s="11">
-        <v>264106</v>
+        <v>264110</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>134</v>
+        <v>298</v>
       </c>
       <c r="C109" s="3">
         <v>30</v>
       </c>
       <c r="D109" s="3" t="s">
-        <v>329</v>
+        <v>131</v>
       </c>
       <c r="E109" s="3" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A110" s="11">
+        <v>264111</v>
+      </c>
+      <c r="B110" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="C110" s="3">
+        <v>1</v>
+      </c>
+      <c r="D110" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="E110" s="3" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A111" s="11">
+        <v>264112</v>
+      </c>
+      <c r="B111" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="C111" s="3">
+        <v>2</v>
+      </c>
+      <c r="D111" s="3" t="s">
+        <v>300</v>
+      </c>
+      <c r="E111" s="3" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A112" s="11">
+        <v>264113</v>
+      </c>
+      <c r="B112" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="C112" s="3">
+        <v>20</v>
+      </c>
+      <c r="D112" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="F109" s="3" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="110" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A110" s="11">
-        <v>264107</v>
-      </c>
-      <c r="B110" s="2" t="s">
-        <v>351</v>
-      </c>
-      <c r="C110" s="3">
-        <v>60</v>
-      </c>
-      <c r="E110" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="F110" s="3" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="111" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A111" s="11">
-        <v>264108</v>
-      </c>
-      <c r="B111" s="2" t="s">
-        <v>353</v>
-      </c>
-      <c r="C111" s="3">
-        <v>6.5</v>
-      </c>
-      <c r="D111" s="3" t="s">
-        <v>329</v>
-      </c>
-      <c r="E111" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="F111" s="3" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="112" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A112" s="11">
-        <v>264109</v>
-      </c>
-      <c r="B112" s="2" t="s">
-        <v>355</v>
-      </c>
-      <c r="C112" s="3">
-        <v>16.5</v>
-      </c>
       <c r="E112" s="3" t="s">
-        <v>353</v>
-      </c>
-      <c r="F112" s="3" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="113" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="113" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A113" s="11">
-        <v>264110</v>
+        <v>264114</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>357</v>
+        <v>306</v>
       </c>
       <c r="C113" s="3">
         <v>30</v>
       </c>
       <c r="D113" s="3" t="s">
-        <v>348</v>
+        <v>304</v>
       </c>
       <c r="E113" s="3" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="114" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A114" s="11">
+        <v>264115</v>
+      </c>
+      <c r="B114" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="C114" s="3">
+        <v>10</v>
+      </c>
+      <c r="D114" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="E114" s="3" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="115" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A115" s="11">
+        <v>264116</v>
+      </c>
+      <c r="B115" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="C115" s="3">
+        <v>16.5</v>
+      </c>
+      <c r="D115" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="F113" s="3" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="114" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A114" s="11">
-        <v>264111</v>
-      </c>
-      <c r="B114" s="2" t="s">
-        <v>359</v>
-      </c>
-      <c r="C114" s="3">
-        <v>1</v>
-      </c>
-      <c r="D114" s="3" t="s">
-        <v>329</v>
-      </c>
-      <c r="E114" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="F114" s="3" t="s">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="115" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A115" s="11">
-        <v>264112</v>
-      </c>
-      <c r="B115" s="2" t="s">
-        <v>361</v>
-      </c>
-      <c r="C115" s="3">
-        <v>2</v>
-      </c>
       <c r="E115" s="3" t="s">
-        <v>359</v>
-      </c>
-      <c r="F115" s="3" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="116" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="116" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A116" s="11">
-        <v>264113</v>
+        <v>264117</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>363</v>
+        <v>139</v>
       </c>
       <c r="C116" s="3">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="D116" s="3" t="s">
-        <v>329</v>
+        <v>138</v>
       </c>
       <c r="E116" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="F116" s="3" t="s">
-        <v>364</v>
-      </c>
-    </row>
-    <row r="117" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="117" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A117" s="11">
-        <v>264114</v>
+        <v>264118</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>365</v>
+        <v>141</v>
       </c>
       <c r="C117" s="3">
         <v>30</v>
       </c>
+      <c r="D117" s="3" t="s">
+        <v>140</v>
+      </c>
       <c r="E117" s="3" t="s">
-        <v>363</v>
-      </c>
-      <c r="F117" s="3" t="s">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="118" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="118" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A118" s="11">
-        <v>264115</v>
+        <v>264119</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>140</v>
+        <v>312</v>
       </c>
       <c r="C118" s="3">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="D118" s="3" t="s">
-        <v>348</v>
+        <v>142</v>
       </c>
       <c r="E118" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="F118" s="3" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="119" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="119" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A119" s="11">
-        <v>264116</v>
+        <v>264120</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>142</v>
+        <v>314</v>
       </c>
       <c r="C119" s="3">
-        <v>16.5</v>
+        <v>12</v>
       </c>
       <c r="D119" s="3" t="s">
-        <v>348</v>
+        <v>143</v>
       </c>
       <c r="E119" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="F119" s="3" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="120" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="120" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A120" s="11">
-        <v>264117</v>
+        <v>264121</v>
       </c>
       <c r="B120" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="C120" s="3">
+        <v>24</v>
+      </c>
+      <c r="D120" s="3" t="s">
+        <v>314</v>
+      </c>
+      <c r="E120" s="3" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="121" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A121" s="11">
+        <v>264122</v>
+      </c>
+      <c r="B121" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="C121" s="3">
+        <v>20</v>
+      </c>
+      <c r="D121" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="C120" s="3">
+      <c r="E121" s="3" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="122" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A122" s="11">
+        <v>264123</v>
+      </c>
+      <c r="B122" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="C122" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D122" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="E122" s="3" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="123" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A123" s="11">
+        <v>264124</v>
+      </c>
+      <c r="B123" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="C123" s="3">
+        <v>30</v>
+      </c>
+      <c r="D123" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="E123" s="3" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="124" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A124" s="11">
+        <v>264125</v>
+      </c>
+      <c r="B124" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="C124" s="3">
         <v>25</v>
       </c>
-      <c r="D120" s="3" t="s">
-        <v>348</v>
-      </c>
-      <c r="E120" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="F120" s="3" t="s">
-        <v>369</v>
-      </c>
-    </row>
-    <row r="121" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A121" s="11">
-        <v>264118</v>
-      </c>
-      <c r="B121" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="C121" s="3">
-        <v>30</v>
-      </c>
-      <c r="D121" s="3" t="s">
-        <v>348</v>
-      </c>
-      <c r="E121" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="F121" s="3" t="s">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="122" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A122" s="11">
-        <v>264119</v>
-      </c>
-      <c r="B122" s="2" t="s">
-        <v>371</v>
-      </c>
-      <c r="C122" s="3">
-        <v>16</v>
-      </c>
-      <c r="D122" s="3" t="s">
-        <v>372</v>
-      </c>
-      <c r="E122" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="F122" s="3" t="s">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="123" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A123" s="11">
-        <v>264120</v>
-      </c>
-      <c r="B123" s="2" t="s">
-        <v>374</v>
-      </c>
-      <c r="C123" s="3">
-        <v>12</v>
-      </c>
-      <c r="D123" s="3" t="s">
-        <v>329</v>
-      </c>
-      <c r="E123" s="3" t="s">
+      <c r="D124" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="F123" s="3" t="s">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="124" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A124" s="11">
-        <v>264121</v>
-      </c>
-      <c r="B124" s="2" t="s">
-        <v>376</v>
-      </c>
-      <c r="C124" s="3">
-        <v>24</v>
-      </c>
       <c r="E124" s="3" t="s">
-        <v>374</v>
-      </c>
-      <c r="F124" s="3" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="125" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="125" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A125" s="11">
-        <v>264122</v>
+        <v>264126</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>378</v>
+        <v>322</v>
       </c>
       <c r="C125" s="3">
+        <v>40</v>
+      </c>
+      <c r="D125" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="E125" s="3" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="126" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A126" s="11">
+        <v>264127</v>
+      </c>
+      <c r="B126" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="C126" s="3">
         <v>20</v>
       </c>
-      <c r="E125" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="F125" s="3" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="126" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A126" s="11">
-        <v>264123</v>
-      </c>
-      <c r="B126" s="2" t="s">
-        <v>380</v>
-      </c>
-      <c r="C126" s="3" t="s">
-        <v>17</v>
+      <c r="D126" s="3" t="s">
+        <v>151</v>
       </c>
       <c r="E126" s="3" t="s">
-        <v>150</v>
-      </c>
-      <c r="F126" s="3" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="127" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A127" s="11">
-        <v>264124</v>
-      </c>
-      <c r="B127" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="C127" s="3">
-        <v>30</v>
-      </c>
-      <c r="E127" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="F127" s="3" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="128" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A128" s="11">
-        <v>264125</v>
-      </c>
-      <c r="B128" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="C128" s="3">
-        <v>25</v>
-      </c>
-      <c r="E128" s="3" t="s">
-        <v>153</v>
-      </c>
-      <c r="F128" s="3" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="129" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A129" s="11">
-        <v>264126</v>
-      </c>
-      <c r="B129" s="2" t="s">
-        <v>382</v>
-      </c>
-      <c r="C129" s="3">
-        <v>40</v>
-      </c>
-      <c r="E129" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="F129" s="3" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="130" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A130" s="11">
-        <v>264127</v>
-      </c>
-      <c r="B130" s="2" t="s">
-        <v>383</v>
-      </c>
-      <c r="C130" s="3">
-        <v>20</v>
-      </c>
-      <c r="E130" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="F130" s="3" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="131" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="127" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A127" s="11"/>
+    </row>
+    <row r="128" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A128" s="11"/>
+    </row>
+    <row r="129" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A129" s="11"/>
+    </row>
+    <row r="130" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A130" s="11"/>
+    </row>
+    <row r="131" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A131" s="11"/>
     </row>
-    <row r="132" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A132" s="11"/>
     </row>
-    <row r="133" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A133" s="11"/>
     </row>
-    <row r="134" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A134" s="11"/>
     </row>
-    <row r="135" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A135" s="11"/>
     </row>
-    <row r="136" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A136" s="11"/>
     </row>
-    <row r="137" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A137" s="11"/>
     </row>
-    <row r="138" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A138" s="11"/>
     </row>
-    <row r="139" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A139" s="11"/>
     </row>
-    <row r="140" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A140" s="11"/>
     </row>
-    <row r="141" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A141" s="11"/>
     </row>
-    <row r="142" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A142" s="11"/>
     </row>
-    <row r="143" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A143" s="11"/>
     </row>
-    <row r="144" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A144" s="11"/>
     </row>
     <row r="145" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -4176,18 +3706,10 @@
     <row r="165" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A165" s="11"/>
     </row>
-    <row r="166" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A166" s="11"/>
-    </row>
-    <row r="167" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A167" s="11"/>
-    </row>
-    <row r="168" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A168" s="11"/>
-    </row>
-    <row r="169" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A169" s="11"/>
-    </row>
+    <row r="166" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="167" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="168" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="169" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="170" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="171" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="172" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
@@ -5023,10 +4545,6 @@
     <row r="1002" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="1003" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="1004" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="1005" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="1006" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="1007" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="1008" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.69999998807907104" right="0.69999998807907104" top="0.75" bottom="0.75" header="0.30000001192092896" footer="0.30000001192092896"/>
